--- a/data/01-12-2025-lookup_types-all.xlsx
+++ b/data/01-12-2025-lookup_types-all.xlsx
@@ -2357,7 +2357,7 @@
         <v>45879</v>
       </c>
       <c r="K3" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2392,7 +2392,7 @@
         <v>45879</v>
       </c>
       <c r="K4" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2427,7 +2427,7 @@
         <v>45879</v>
       </c>
       <c r="K5" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2462,7 +2462,7 @@
         <v>45879</v>
       </c>
       <c r="K6" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2497,7 +2497,7 @@
         <v>45879</v>
       </c>
       <c r="K7" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2532,7 +2532,7 @@
         <v>45879</v>
       </c>
       <c r="K8" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2567,7 +2567,7 @@
         <v>45879</v>
       </c>
       <c r="K9" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2602,7 +2602,7 @@
         <v>45891</v>
       </c>
       <c r="K10" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2637,7 +2637,7 @@
         <v>45890</v>
       </c>
       <c r="K11" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2672,7 +2672,7 @@
         <v>45934</v>
       </c>
       <c r="K12" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2707,7 +2707,7 @@
         <v>45879</v>
       </c>
       <c r="K13" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2742,7 +2742,7 @@
         <v>45879</v>
       </c>
       <c r="K14" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2777,7 +2777,7 @@
         <v>45890</v>
       </c>
       <c r="K15" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2812,7 +2812,7 @@
         <v>45962</v>
       </c>
       <c r="K16" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2847,7 +2847,7 @@
         <v>45962</v>
       </c>
       <c r="K17" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2882,7 +2882,7 @@
         <v>45975</v>
       </c>
       <c r="K18" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -6387,7 +6387,7 @@
         <v>45984</v>
       </c>
       <c r="K119" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
